--- a/inst/resources/variable_schema_data_individual_roster_template.xlsx
+++ b/inst/resources/variable_schema_data_individual_roster_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SaeedRAHMAN\Documents\GitHub\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1EF71B-9D9F-444E-808A-F8377E8A0D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD058B3F-2D1F-4DE1-936E-191DB8262B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -847,9 +847,6 @@
     <t>weight</t>
   </si>
   <si>
-    <t>weight,sampling_weight,survey_weight,wt</t>
-  </si>
-  <si>
     <t>Sampling Weight</t>
   </si>
   <si>
@@ -977,6 +974,9 @@
   </si>
   <si>
     <t>المنطقة الإدارية 4</t>
+  </si>
+  <si>
+    <t>weight,sampling_weight,survey_weight,wt,weights</t>
   </si>
 </sst>
 </file>
@@ -1841,19 +1841,19 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
+        <v>318</v>
+      </c>
+      <c r="L15" t="s">
         <v>275</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>276</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>277</v>
       </c>
-      <c r="N15" t="s">
+      <c r="R15" t="s">
         <v>278</v>
-      </c>
-      <c r="R15" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -1861,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1873,19 +1873,19 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
+        <v>280</v>
+      </c>
+      <c r="L16" t="s">
         <v>281</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>282</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>283</v>
       </c>
-      <c r="N16" t="s">
+      <c r="R16" t="s">
         <v>284</v>
-      </c>
-      <c r="R16" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1905,19 +1905,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
+        <v>286</v>
+      </c>
+      <c r="L17" t="s">
         <v>287</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>288</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>289</v>
       </c>
-      <c r="N17" t="s">
+      <c r="R17" t="s">
         <v>290</v>
-      </c>
-      <c r="R17" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1925,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1937,19 +1937,19 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L18" t="s">
+        <v>287</v>
+      </c>
+      <c r="M18" t="s">
         <v>288</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>289</v>
       </c>
-      <c r="N18" t="s">
+      <c r="R18" t="s">
         <v>290</v>
-      </c>
-      <c r="R18" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1957,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1969,19 +1969,19 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
+        <v>293</v>
+      </c>
+      <c r="L19" t="s">
         <v>294</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>295</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>296</v>
       </c>
-      <c r="N19" t="s">
+      <c r="R19" t="s">
         <v>297</v>
-      </c>
-      <c r="R19" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1989,7 +1989,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2001,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="s">
+        <v>299</v>
+      </c>
+      <c r="L20" t="s">
         <v>300</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>301</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>302</v>
-      </c>
-      <c r="N20" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2018,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2030,16 +2030,16 @@
         <v>0</v>
       </c>
       <c r="J21" t="s">
+        <v>304</v>
+      </c>
+      <c r="L21" t="s">
         <v>305</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>306</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>307</v>
-      </c>
-      <c r="N21" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2059,16 +2059,16 @@
         <v>0</v>
       </c>
       <c r="J22" t="s">
+        <v>309</v>
+      </c>
+      <c r="L22" t="s">
         <v>310</v>
       </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>311</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>312</v>
-      </c>
-      <c r="N22" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2076,7 +2076,7 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2088,16 +2088,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="s">
+        <v>314</v>
+      </c>
+      <c r="L23" t="s">
         <v>315</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>316</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>317</v>
-      </c>
-      <c r="N23" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
